--- a/testakten/erbrecht-unternehmernachfolge-testamentsvollstrecker-wuerzburg/xlsx/nachlass_und_gmbh_wertband.xlsx
+++ b/testakten/erbrecht-unternehmernachfolge-testamentsvollstrecker-wuerzburg/xlsx/nachlass_und_gmbh_wertband.xlsx
@@ -8,9 +8,14 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nachlass" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pflichtteil" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pflichtteil Szenarien" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bank Liquidität" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nachlass'!$A$1:$G$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pflichtteil Szenarien'!$A$1:$F$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Bank Liquidität'!$A$1:$G$5</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -18,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,16 +31,31 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0017324D"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +63,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00CFD6DA"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,128 +445,243 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="41" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Position</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Wert niedrig</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Wert mittel</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Wert hoch</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Beleg</t>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Wert niedrig EUR</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Wert mittel EUR</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Wert hoch EUR</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Quelle</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Offener Punkt</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>GmbH-Anteile</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>3200000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>4200000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>5600000</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>EBIT-Multiple offen</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>GmbH-Anteile 72 Prozent</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>9800000</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>12200000</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>14600000</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Vollstreckerbericht / Gutachterangebote</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Bewertung offen</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Planung, Kundenkonzentration, Investition</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Privathaus</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>780000</v>
-      </c>
-      <c r="C3" t="n">
-        <v>820000</v>
-      </c>
-      <c r="D3" t="n">
-        <v>850000</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Gutachterkurzbrief</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Wohnhaus Höchberg</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>1080000</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>1150000</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>1220000</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Ortstermin 09.06.2026</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Gutachtenentwurf</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Sanierungsbedarf</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Depot</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>420000</v>
-      </c>
-      <c r="C4" t="n">
-        <v>420000</v>
-      </c>
-      <c r="D4" t="n">
-        <v>420000</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Bank</t>
+      <c r="B4" s="2" t="n">
+        <v>1840000</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>1840000</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>1840000</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Bankbestätigung</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>bestätigt</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Stichtagskurse abgelegt</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Darlehen GmbH</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>-310000</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-310000</v>
-      </c>
-      <c r="D5" t="n">
-        <v>-310000</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Vertrag</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Verrechnungskonto GmbH</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>128000</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>218400</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>308400</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Kontoblätter</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Abstimmung offen</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Reisekosten und Ausschüttung</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Weitere Aktiva</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>310000</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>390000</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>470000</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Inventar</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>teilweise</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Oldtimer und Bank</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Nachlassverbindlichkeiten</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>-540000</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>-486000</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>-430000</v>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Steuer und Darlehen</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>teilweise</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Bescheide</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -546,92 +692,311 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Szenario</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Reinnachlass</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Reinnachlass EUR</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Quote Tilo</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Anspruch vor Einreden</t>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Rechnerischer Betrag EUR</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Liquiditätsannahme</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Kein Anerkenntnis</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>niedrig</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>4090000</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1/4</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>1022500</v>
+      <c r="B2" s="2">
+        <f>Nachlass!B2+Nachlass!B3+Nachlass!B4+Nachlass!B5+Nachlass!B6+Nachlass!B7</f>
+        <v/>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D2" s="2">
+        <f>B2*C2</f>
+        <v/>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Stundung 36 Monate offen</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Arbeitswert</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>mittel</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>5130000</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1/4</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>1282500</v>
+      <c r="B3" s="2">
+        <f>Nachlass!C2+Nachlass!C3+Nachlass!C4+Nachlass!C5+Nachlass!C6+Nachlass!C7</f>
+        <v/>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D3" s="2">
+        <f>B3*C3</f>
+        <v/>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Teilzahlung nach Bewertung</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Arbeitswert</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>hoch</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>6560000</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1/4</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>1640000</v>
+      <c r="B4" s="2">
+        <f>Nachlass!D2+Nachlass!D3+Nachlass!D4+Nachlass!D5+Nachlass!D6+Nachlass!D7</f>
+        <v/>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D4" s="2">
+        <f>B4*C4</f>
+        <v/>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>externe Finanzierung nötig</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Arbeitswert</t>
+        </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F4"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Woche</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Anfangsbestand EUR</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Einzahlungen EUR</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Auszahlungen EUR</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Endbestand EUR</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Mindestreserve EUR</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Quelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>29.06.-05.07.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>1720000</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>1380000</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>-1210000</v>
+      </c>
+      <c r="E2" s="2">
+        <f>B2+C2+D2</f>
+        <v/>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Controlling v1.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>06.07.-12.07.</t>
+        </is>
+      </c>
+      <c r="B3" s="2">
+        <f>E2</f>
+        <v/>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>910000</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>-990000</v>
+      </c>
+      <c r="E3" s="2">
+        <f>B3+C3+D3</f>
+        <v/>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Auftragseingang</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>13.07.-19.07.</t>
+        </is>
+      </c>
+      <c r="B4" s="2">
+        <f>E3</f>
+        <v/>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>740000</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>-1180000</v>
+      </c>
+      <c r="E4" s="2">
+        <f>B4+C4+D4</f>
+        <v/>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Material und Löhne</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>20.07.-26.07.</t>
+        </is>
+      </c>
+      <c r="B5" s="2">
+        <f>E4</f>
+        <v/>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>1620000</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>-1080000</v>
+      </c>
+      <c r="E5" s="2">
+        <f>B5+C5+D5</f>
+        <v/>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Kundenzahlungen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>